--- a/dist/Energofish_partner_hirlevel_minta.xlsx
+++ b/dist/Energofish_partner_hirlevel_minta.xlsx
@@ -252,7 +252,7 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Kötelező. A címzett e-mail címe, erre készül a hírlevél.</t>
+        <t>Kötelező. A címzett e-mail címe. Több cím pontosvesszővel elválasztva is megadható.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
